--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486706_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486706_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2379</v>
+        <v>8.902699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.545</v>
+        <v>5.6071</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6929</v>
+        <v>3.2956</v>
       </c>
       <c r="G2" t="n">
         <v>6.3715</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6733</v>
+        <v>0.3382</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0279</v>
+        <v>0.0342</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7012</v>
+        <v>0.3039</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.3783</v>
+        <v>6.7454</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9188</v>
+        <v>3.3603</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4596</v>
+        <v>3.3851</v>
       </c>
       <c r="G3" t="n">
         <v>3.0351</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4398</v>
+        <v>0.8069</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3786</v>
+        <v>0.8202</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0612</v>
+        <v>-0.0133</v>
       </c>
       <c r="V3" t="n">
         <v>0.2004</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3654</v>
+        <v>6.4825</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9622</v>
+        <v>2.9551</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4032</v>
+        <v>3.5273</v>
       </c>
       <c r="G4" t="n">
         <v>4.6</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9377</v>
+        <v>0.1794</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>0.4686</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4134</v>
+        <v>-0.2892</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6138</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0335</v>
+        <v>5.3536</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4926</v>
+        <v>2.7134</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5409</v>
+        <v>2.6403</v>
       </c>
       <c r="G5" t="n">
         <v>0.1478</v>
@@ -844,13 +844,13 @@
         <v>2.51</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4578</v>
+        <v>-0.1378</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2486</v>
+        <v>-0.0279</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2092</v>
+        <v>-0.1099</v>
       </c>
       <c r="V5" t="n">
         <v>3.0266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2121</v>
+        <v>4.8341</v>
       </c>
       <c r="E6" t="n">
-        <v>2.297</v>
+        <v>2.8693</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9151</v>
+        <v>1.9647</v>
       </c>
       <c r="G6" t="n">
         <v>2.9166</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3183</v>
+        <v>-0.6964</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6622</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6561</v>
+        <v>-0.6065</v>
       </c>
       <c r="V6" t="n">
         <v>1.8415</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7584</v>
+        <v>3.0315</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2088</v>
+        <v>0.1635</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9673</v>
+        <v>2.8679</v>
       </c>
       <c r="G7" t="n">
         <v>3.0958</v>
@@ -1000,13 +1000,13 @@
         <v>2.1239</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0994</v>
+        <v>0.3725</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0279</v>
+        <v>0.3445</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1273</v>
+        <v>0.028</v>
       </c>
       <c r="V7" t="n">
         <v>0.5286</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7309</v>
+        <v>2.9543</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-0.3317</v>
       </c>
       <c r="F8" t="n">
-        <v>3.435</v>
+        <v>3.286</v>
       </c>
       <c r="G8" t="n">
         <v>0.7517</v>
@@ -1078,13 +1078,13 @@
         <v>2.3169</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5352</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.11</v>
+        <v>0.4824</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4252</v>
+        <v>0.2762</v>
       </c>
       <c r="V8" t="n">
         <v>0.2856</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4852</v>
+        <v>1.2067</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1654</v>
+        <v>0.8621</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3198</v>
+        <v>0.3447</v>
       </c>
       <c r="G9" t="n">
         <v>0.3655</v>
@@ -1156,13 +1156,13 @@
         <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5405</v>
+        <v>0.262</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5239</v>
+        <v>0.2206</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5561</v>
+        <v>0.4885</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8277</v>
+        <v>-1.8208</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3838</v>
+        <v>2.3093</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1667</v>
@@ -1234,13 +1234,13 @@
         <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0495</v>
+        <v>-0.1171</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1934</v>
+        <v>-0.1865</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1439</v>
+        <v>0.0694</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. OMERAGIC ALIC</t>
+          <t>J. ORAMAS MARTEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3075</v>
+        <v>-1.0377</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4265</v>
+        <v>-2.9995</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1191</v>
+        <v>1.9619</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.634</v>
+        <v>-0.297</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1104</v>
+        <v>0.3789</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7444</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7159</v>
+        <v>-0.8617</v>
       </c>
       <c r="K11" t="n">
-        <v>1.042</v>
+        <v>-0.1722</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.7579</v>
+        <v>-0.6895</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0819</v>
+        <v>0.5646</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0684</v>
+        <v>0.5511</v>
       </c>
       <c r="O11" t="n">
         <v>0.0135</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R11" t="n">
-        <v>2.51</v>
+        <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1913</v>
+        <v>-0.262</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3786</v>
+        <v>-0.014</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1873</v>
+        <v>-0.248</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2856</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ORAMAS MARTEL</t>
+          <t>A. OMERAGIC ALIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.344</v>
+        <v>-1.8162</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9582</v>
+        <v>-3.9849</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6142</v>
+        <v>2.1687</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.297</v>
+        <v>-1.634</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3789</v>
+        <v>1.1104</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-2.7444</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8617</v>
+        <v>-1.7159</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1722</v>
+        <v>1.042</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6895</v>
+        <v>-2.7579</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5646</v>
+        <v>0.0819</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5511</v>
+        <v>0.0684</v>
       </c>
       <c r="O12" t="n">
         <v>0.0135</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5683</v>
+        <v>0.6826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0273</v>
+        <v>0.8202</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5956</v>
+        <v>-0.1376</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.2221</v>
+        <v>-3.3298</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.7439</v>
+        <v>-3.9509</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5218</v>
+        <v>0.6211</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4618</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7337</v>
+        <v>0.1586</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6347</v>
+        <v>0.1584</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09909999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7989</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.8842</v>
+        <v>33.8156</v>
       </c>
       <c r="E14" t="n">
-        <v>3.511799999999999</v>
+        <v>5.443000000000004</v>
       </c>
       <c r="F14" t="n">
-        <v>28.3727</v>
+        <v>28.3726</v>
       </c>
       <c r="G14" t="n">
         <v>16.7245</v>
@@ -1528,7 +1528,7 @@
         <v>-10.3761</v>
       </c>
       <c r="M14" t="n">
-        <v>8.126900000000001</v>
+        <v>8.126899999999999</v>
       </c>
       <c r="N14" t="n">
         <v>5.1661</v>
@@ -1543,16 +1543,16 @@
         <v>-14.481</v>
       </c>
       <c r="R14" t="n">
-        <v>25.10020000000001</v>
+        <v>25.1002</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4142000000000001</v>
+        <v>2.3455</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0994</v>
+        <v>3.0308</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6853</v>
+        <v>-0.6854</v>
       </c>
       <c r="V14" t="n">
         <v>4.126500000000002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BIURRUN SANTAMARIA</t>
+          <t>G. COMACHIO COACHMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6195</v>
+        <v>1.3418</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2261</v>
+        <v>-0.7123</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3934</v>
+        <v>2.0541</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0739</v>
+        <v>-0.1614</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.8686</v>
+        <v>-1.9383</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9426</v>
+        <v>1.7768</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2818</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2818</v>
+        <v>-0.2134</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5636</v>
+        <v>0.1221</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2079</v>
+        <v>-0.0701</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5868</v>
+        <v>-1.7249</v>
       </c>
       <c r="O15" t="n">
-        <v>1.379</v>
+        <v>1.6548</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5446</v>
+        <v>-0.5792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1514</v>
+        <v>0.1517</v>
       </c>
       <c r="T15" t="n">
-        <v>1.489</v>
+        <v>-0.0418</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6624</v>
+        <v>0.1934</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. COMACHIO COACHMAN</t>
+          <t>A. BIURRUN SANTAMARIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4232</v>
+        <v>0.5438</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3329</v>
+        <v>0.3988</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7561</v>
+        <v>0.145</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1614</v>
+        <v>1.0739</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9383</v>
+        <v>-2.8686</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7768</v>
+        <v>3.9426</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.09130000000000001</v>
+        <v>1.2818</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2134</v>
+        <v>-1.2818</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>2.5636</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0701</v>
+        <v>-0.2079</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7249</v>
+        <v>-1.5868</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6548</v>
+        <v>1.379</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.5792</v>
+        <v>-1.5446</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7669</v>
+        <v>1.0757</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6623</v>
+        <v>0.6616</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1045</v>
+        <v>0.4141</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6906</v>
+        <v>-0.3637</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0805</v>
+        <v>-2.9771</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3899</v>
+        <v>2.6134</v>
       </c>
       <c r="G17" t="n">
         <v>-1.0407</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2373</v>
+        <v>0.0896</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0555</v>
+        <v>0.0479</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1817</v>
+        <v>0.0417</v>
       </c>
       <c r="V17" t="n">
         <v>3.0973</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1177</v>
+        <v>-1.3701</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.7015</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9227</v>
+        <v>-2.0716</v>
       </c>
       <c r="G18" t="n">
         <v>0.2528</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3697</v>
+        <v>0.1172</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2756</v>
+        <v>0.1721</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0941</v>
+        <v>-0.0549</v>
       </c>
       <c r="V18" t="n">
         <v>-2.5125</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4911</v>
+        <v>-3.0181</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.2633</v>
+        <v>-2.953</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2278</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-3.5057</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8937</v>
+        <v>-0.4207</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3866</v>
+        <v>-0.0764</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.507</v>
+        <v>-0.3443</v>
       </c>
       <c r="V19" t="n">
         <v>-0.0571</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6106</v>
+        <v>-3.0605</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0131</v>
+        <v>-3.2892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4025</v>
+        <v>0.2287</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2988</v>
@@ -2014,13 +2014,13 @@
         <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6675</v>
+        <v>-0.1173</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0209</v>
+        <v>-0.297</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3535</v>
+        <v>0.1796</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7136</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8432</v>
+        <v>-3.4943</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3248</v>
+        <v>-4.0145</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4816</v>
+        <v>0.5202</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5153</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1822</v>
+        <v>0.531</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1375</v>
+        <v>0.4478</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0446</v>
+        <v>0.0832</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. FERMIN DE LUNA</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1423</v>
+        <v>-6.2015</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1396</v>
+        <v>-4.2253</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0026</v>
+        <v>-1.9761</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.2193</v>
+        <v>-4.7944</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.2691</v>
+        <v>-3.7794</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0497</v>
+        <v>-1.015</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2248</v>
+        <v>-3.3521</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5783</v>
+        <v>-2.0545</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6465</v>
+        <v>-1.2976</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9945</v>
+        <v>-1.4423</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.6908</v>
+        <v>-1.7249</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6962</v>
+        <v>0.2826</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6685</v>
+        <v>0.1931</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8034</v>
+        <v>-0.3724</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3988</v>
+        <v>-0.1934</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5954</v>
+        <v>-0.179</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9421</v>
+        <v>-1.2277</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5712</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>J. FERMIN DE LUNA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5792</v>
+        <v>-6.8701</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.639</v>
+        <v>-5.1047</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9402</v>
+        <v>-1.7654</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.7944</v>
+        <v>-4.2193</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.7794</v>
+        <v>-4.2691</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.015</v>
+        <v>0.0497</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.3521</v>
+        <v>-2.2248</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.0545</v>
+        <v>-1.5783</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2976</v>
+        <v>-0.6465</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4423</v>
+        <v>-1.9945</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7249</v>
+        <v>-2.6908</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2826</v>
+        <v>0.6962</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1931</v>
+        <v>-3.6685</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R23" t="n">
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7502</v>
+        <v>0.0757</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6071</v>
+        <v>0.4338</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1431</v>
+        <v>-0.3581</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2277</v>
+        <v>0.9421</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5133</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.452299999999999</v>
+        <v>-8.7021</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6105</v>
+        <v>-6.1968</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8418</v>
+        <v>-2.5052</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5155</v>
@@ -2326,13 +2326,13 @@
         <v>0.7723</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6054</v>
+        <v>-0.8551</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.883</v>
+        <v>-0.4693</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7224</v>
+        <v>-0.3858</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2422</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.8843</v>
+        <v>-31.1948</v>
       </c>
       <c r="E25" t="n">
-        <v>-28.3727</v>
+        <v>-28.3726</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.5116</v>
+        <v>-2.822</v>
       </c>
       <c r="G25" t="n">
         <v>-16.7244</v>
@@ -2404,13 +2404,13 @@
         <v>14.4809</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4142999999999999</v>
+        <v>0.2754000000000003</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6855000000000002</v>
+        <v>0.6853</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0995</v>
+        <v>-0.4100999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-4.1264</v>
